--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251108_201245.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251108_201245.xlsx
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251108_201245.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251108_201245.xlsx
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
